--- a/remotes/keymapper/rs90/KeyCodes RS90.xlsx
+++ b/remotes/keymapper/rs90/KeyCodes RS90.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS90" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw keys" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1047,17 +1048,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>KEYCODE_EQUALS</t>
+          <t>KEYCODE_F12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1069,38 +1070,277 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Home (F2) long-press</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>132</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KEYCODE_F2</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KEYCODE_EQUALS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Dot ••• (F11) long-press</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>141</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>KEYCODE_F11</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>87</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Run Harmonium IME-Fix</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>com.skavan.imefix</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>global</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Physical key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Emits</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>What Harmonium does</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D-pad ▲ ▼ ◀ ▶</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arrow keys</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>move panel focus · drive the device on TV pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OK (center)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enter</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>activate the focused card · hold = grab the D-pad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Power (F1) tap</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>power — end/start the page's activity (confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Home (F2) tap</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Harmonium home — up one level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Channel ▲/▼ tap</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PageUp / PageDown</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jump sections · on TV pages: borrow the D-pad for the panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mic (F5)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rs90 profile: `mic` — bindable in the Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ScreenCast (F6)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rs90 profile: `screencast` — bindable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Source (F7)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>rs90 profile: `source` — bindable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Settings (F8)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>rs90 profile: `settings` — bindable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REW / Play-Pause / FWD tap</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MediaRewind / MediaPlayPause / MediaFastForward</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>prev / play-pause / next on the running music</t>
         </is>
       </c>
     </row>
